--- a/GameData/tables/09_Gear.xlsx
+++ b/GameData/tables/09_Gear.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gear_surv" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'gear'!$A$1:$O$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'gear_surv'!$A$1:$F$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'gear'!$A$1:$O$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'gear_surv'!$A$1:$F$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -526,13 +526,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O23"/>
+  <dimension ref="A1:O27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11.6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -1799,8 +1799,260 @@
         <v>1.4</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="5" t="n">
+        <v>4013</v>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>excl</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>blender</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>gear.4013.name</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>gear.4013.eff</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>execBonus</t>
+        </is>
+      </c>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>add</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M24" s="6" t="inlineStr">
+        <is>
+          <t>grindRadius</t>
+        </is>
+      </c>
+      <c r="N24" s="6" t="inlineStr">
+        <is>
+          <t>add</t>
+        </is>
+      </c>
+      <c r="O24" s="5" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n">
+        <v>4014</v>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>excl</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>purifier</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>gear.4014.name</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>gear.4014.eff</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>airMul</t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>add</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M25" s="6" t="inlineStr">
+        <is>
+          <t>skillDmg</t>
+        </is>
+      </c>
+      <c r="N25" s="6" t="inlineStr">
+        <is>
+          <t>mul</t>
+        </is>
+      </c>
+      <c r="O25" s="5" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n">
+        <v>4015</v>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>excl</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>router</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>gear.4015.name</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>gear.4015.eff</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>chainN</t>
+        </is>
+      </c>
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t>add</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" s="6" t="inlineStr">
+        <is>
+          <t>chainDecay</t>
+        </is>
+      </c>
+      <c r="N26" s="6" t="inlineStr">
+        <is>
+          <t>add</t>
+        </is>
+      </c>
+      <c r="O26" s="5" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n">
+        <v>4016</v>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>excl</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>tv</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>gear.4016.name</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>gear.4016.eff</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>adVuln</t>
+        </is>
+      </c>
+      <c r="K27" s="6" t="inlineStr">
+        <is>
+          <t>add</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M27" s="6" t="inlineStr">
+        <is>
+          <t>dur</t>
+        </is>
+      </c>
+      <c r="N27" s="6" t="inlineStr">
+        <is>
+          <t>add</t>
+        </is>
+      </c>
+      <c r="O27" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O23"/>
+  <autoFilter ref="A1:O27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1811,11 +2063,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11.6" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -2726,8 +2978,232 @@
         <v>1.4</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="5" t="n">
+        <v>4013</v>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>blender</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>comp</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>dmg</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>mul</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="n">
+        <v>4013</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>blender</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>comp</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>radius</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>add</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="n">
+        <v>4014</v>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>purifier</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>comp</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>dmg</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>mul</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="n">
+        <v>4014</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>purifier</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>comp</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>add</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n">
+        <v>4015</v>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>router</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>comp</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>dmg</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>mul</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="n">
+        <v>4015</v>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>router</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>comp</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>add</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="n">
+        <v>4016</v>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>tv</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>comp</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>freeze</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>add</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="n">
+        <v>4016</v>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>tv</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>comp</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>dmg</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>mul</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F32"/>
+  <autoFilter ref="A1:F40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>